--- a/output/60bom_BOM_Report.xlsx
+++ b/output/60bom_BOM_Report.xlsx
@@ -1089,7 +1089,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-24T08:28:28+00:00  |  Rules: E:\GitHub\BOM_Normalization_Tool\config\default_rules.json; runtime near-value override  |  Platform: 2.0.0</t>
+          <t>Generated: 2026-07-24T09:03:29+00:00  |  Rules: E:\GitHub\BOM_Normalization_Tool\config\default_rules.json; runtime near-value override  |  Platform: 2.0.0</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>2026-07-24T08:28:28+00:00</t>
+          <t>2026-07-24T09:03:29+00:00</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
           <t>11.8kOhm</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="16" t="n">
@@ -6348,10 +6348,10 @@
       <c r="G2" s="16" t="inlineStr">
         <is>
           <t>🟠 Near Value 11.8kΩ ➔ 12kΩ (-1.66%)
-Target Value : 12kΩ
-Package : 0402
-Qty : 5 pcs
-Difference : -1.66%</t>
+12kΩ
+0402
+Qty 5
+-1.66%</t>
         </is>
       </c>
       <c r="H2" s="16" t="inlineStr">
@@ -6366,7 +6366,7 @@
           <t>2.67kOhm</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="15" t="n">
@@ -6389,14 +6389,14 @@
       <c r="G3" s="15" t="inlineStr">
         <is>
           <t>🟠 Near Value 2.67kΩ ➔ 2.7kΩ (-1.11%)
-Target Value : 2.7kΩ
-Package : 0402
-Qty : 12 pcs
-Difference : -1.11%
-Target Value : 2.74kΩ
-Package : 0402
-Qty : 1 pcs
-Difference : -2.55%</t>
+2.7kΩ
+0402
+Qty 12
+-1.11%
+2.74kΩ
+0402
+Qty 1
+-2.55%</t>
         </is>
       </c>
       <c r="H3" s="15" t="inlineStr">
@@ -6411,7 +6411,7 @@
           <t>2.74kOhm</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="16" t="n">
@@ -6434,14 +6434,14 @@
       <c r="G4" s="16" t="inlineStr">
         <is>
           <t>🟠 Near Value 2.74kΩ ➔ 2.7kΩ (+1.48%)
-Target Value : 2.7kΩ
-Package : 0402
-Qty : 12 pcs
-Difference : +1.48%
-Target Value : 2.67kΩ
-Package : 0402
-Qty : 1 pcs
-Difference : +2.62%</t>
+2.7kΩ
+0402
+Qty 12
++1.48%
+2.67kΩ
+0402
+Qty 1
++2.62%</t>
         </is>
       </c>
       <c r="H4" s="16" t="inlineStr">
@@ -6456,7 +6456,7 @@
           <t>20.5kOhm</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="15" t="n">
@@ -6479,10 +6479,10 @@
       <c r="G5" s="15" t="inlineStr">
         <is>
           <t>🟠 Near Value 20.5kΩ ➔ 20kΩ (+2.5%)
-Target Value : 20kΩ
-Package : 0402
-Qty : 9 pcs
-Difference : +2.5%</t>
+20kΩ
+0402
+Qty 9
++2.5%</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
@@ -6497,7 +6497,7 @@
           <t>22.1kOhm</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="16" t="n">
@@ -6520,10 +6520,10 @@
       <c r="G6" s="16" t="inlineStr">
         <is>
           <t>🟠 Near Value 22.1kΩ ➔ 22kΩ (+0.45%)
-Target Value : 22kΩ
-Package : 0402
-Qty : 2 pcs
-Difference : +0.45%</t>
+22kΩ
+0402
+Qty 2
++0.45%</t>
         </is>
       </c>
       <c r="H6" s="16" t="inlineStr">
@@ -6538,7 +6538,7 @@
           <t>39.2kOhm</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="15" t="n">
@@ -6561,10 +6561,10 @@
       <c r="G7" s="15" t="inlineStr">
         <is>
           <t>🟠 Near Value 39.2kΩ ➔ 40.2kΩ (-2.49%)
-Target Value : 40.2kΩ
-Package : 0402
-Qty : 2 pcs
-Difference : -2.49%</t>
+40.2kΩ
+0402
+Qty 2
+-2.49%</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
@@ -6579,7 +6579,7 @@
           <t>51Ohm</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="16" t="n">
@@ -6602,10 +6602,10 @@
       <c r="G8" s="16" t="inlineStr">
         <is>
           <t>🟠 Near Value 51Ω ➔ 49.9Ω (+2.2%)
-Target Value : 49.9Ω
-Package : 0402
-Qty : 8 pcs
-Difference : +2.2%</t>
+49.9Ω
+0402
+Qty 8
++2.2%</t>
         </is>
       </c>
       <c r="H8" s="16" t="inlineStr">
@@ -6620,7 +6620,7 @@
           <t>10.2kOhm</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="15" t="n">
@@ -6643,14 +6643,14 @@
       <c r="G9" s="15" t="inlineStr">
         <is>
           <t>🟠 Near Value 10.2kΩ ➔ 10kΩ (+2%)
-Target Value : 10kΩ
-Package : 0402
-Qty : 62 pcs
-Difference : +2%
-Target Value : 10.5kΩ
-Package : 0402
-Qty : 2 pcs
-Difference : -2.86%</t>
+10kΩ
+0402
+Qty 62
++2%
+10.5kΩ
+0402
+Qty 2
+-2.86%</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
@@ -6665,7 +6665,7 @@
           <t>10Ohm</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="16" t="n">
@@ -6702,7 +6702,7 @@
           <t>8.2kOhm</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C11" s="15" t="n">
@@ -6739,7 +6739,7 @@
           <t>1Ohm</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="16" t="n">
@@ -6776,7 +6776,7 @@
           <t>4.7Ohm</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="15" t="n">
@@ -6813,7 +6813,7 @@
           <t>330Ohm</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C14" s="16" t="n">
@@ -6850,7 +6850,7 @@
           <t>100Ohm</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="15" t="n">
@@ -6887,7 +6887,7 @@
           <t>2.2Ohm</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C16" s="16" t="n">
@@ -6924,7 +6924,7 @@
           <t>1kOhm</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C17" s="15" t="n">
@@ -6961,7 +6961,7 @@
           <t>100kOhm</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C18" s="16" t="n">
@@ -6998,7 +6998,7 @@
           <t>0Ohm</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C19" s="15" t="n">
@@ -7031,25 +7031,54 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H19"/>
+  <conditionalFormatting sqref="E2:E19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>LEFT($E2,LEN("🟢 Merge"))="🟢 Merge"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>LEFT($E2,LEN("🟡 Review"))="🟡 Review"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>LEFT($E2,LEN("⚪ Keep"))="⚪ Keep"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7166,10 +7195,10 @@
       <c r="I2" s="24" t="inlineStr">
         <is>
           <t>🟠 Near Value 11.8kΩ ➔ 12kΩ (-1.66%)
-Target Value : 12kΩ
-Package : 0402
-Qty : 5 pcs
-Difference : -1.66%</t>
+12kΩ
+0402
+Qty 5
+-1.66%</t>
         </is>
       </c>
       <c r="J2" s="24" t="inlineStr"/>
@@ -7393,14 +7422,14 @@
       <c r="I8" s="24" t="inlineStr">
         <is>
           <t>🟠 Near Value 2.67kΩ ➔ 2.7kΩ (-1.11%)
-Target Value : 2.7kΩ
-Package : 0402
-Qty : 12 pcs
-Difference : -1.11%
-Target Value : 2.74kΩ
-Package : 0402
-Qty : 1 pcs
-Difference : -2.55%</t>
+2.7kΩ
+0402
+Qty 12
+-1.11%
+2.74kΩ
+0402
+Qty 1
+-2.55%</t>
         </is>
       </c>
       <c r="J8" s="24" t="inlineStr"/>
@@ -7715,14 +7744,14 @@
       <c r="I16" s="24" t="inlineStr">
         <is>
           <t>🟠 Near Value 2.74kΩ ➔ 2.7kΩ (+1.48%)
-Target Value : 2.7kΩ
-Package : 0402
-Qty : 12 pcs
-Difference : +1.48%
-Target Value : 2.67kΩ
-Package : 0402
-Qty : 1 pcs
-Difference : +2.62%</t>
+2.7kΩ
+0402
+Qty 12
++1.48%
+2.67kΩ
+0402
+Qty 1
++2.62%</t>
         </is>
       </c>
       <c r="J16" s="24" t="inlineStr"/>
@@ -8128,10 +8157,10 @@
       <c r="I26" s="24" t="inlineStr">
         <is>
           <t>🟠 Near Value 20.5kΩ ➔ 20kΩ (+2.5%)
-Target Value : 20kΩ
-Package : 0402
-Qty : 9 pcs
-Difference : +2.5%</t>
+20kΩ
+0402
+Qty 9
++2.5%</t>
         </is>
       </c>
       <c r="J26" s="24" t="inlineStr"/>
@@ -8355,10 +8384,10 @@
       <c r="I32" s="24" t="inlineStr">
         <is>
           <t>🟠 Near Value 22.1kΩ ➔ 22kΩ (+0.45%)
-Target Value : 22kΩ
-Package : 0402
-Qty : 2 pcs
-Difference : +0.45%</t>
+22kΩ
+0402
+Qty 2
++0.45%</t>
         </is>
       </c>
       <c r="J32" s="24" t="inlineStr"/>
@@ -8582,10 +8611,10 @@
       <c r="I38" s="24" t="inlineStr">
         <is>
           <t>🟠 Near Value 39.2kΩ ➔ 40.2kΩ (-2.49%)
-Target Value : 40.2kΩ
-Package : 0402
-Qty : 2 pcs
-Difference : -2.49%</t>
+40.2kΩ
+0402
+Qty 2
+-2.49%</t>
         </is>
       </c>
       <c r="J38" s="24" t="inlineStr"/>
@@ -8900,10 +8929,10 @@
       <c r="I46" s="24" t="inlineStr">
         <is>
           <t>🟠 Near Value 51Ω ➔ 49.9Ω (+2.2%)
-Target Value : 49.9Ω
-Package : 0402
-Qty : 8 pcs
-Difference : +2.2%</t>
+49.9Ω
+0402
+Qty 8
++2.2%</t>
         </is>
       </c>
       <c r="J46" s="24" t="inlineStr"/>
@@ -9127,14 +9156,14 @@
       <c r="I52" s="24" t="inlineStr">
         <is>
           <t>🟠 Near Value 10.2kΩ ➔ 10kΩ (+2%)
-Target Value : 10kΩ
-Package : 0402
-Qty : 62 pcs
-Difference : +2%
-Target Value : 10.5kΩ
-Package : 0402
-Qty : 2 pcs
-Difference : -2.86%</t>
+10kΩ
+0402
+Qty 62
++2%
+10.5kΩ
+0402
+Qty 2
+-2.86%</t>
         </is>
       </c>
       <c r="J52" s="24" t="inlineStr"/>

--- a/output/60bom_BOM_Report.xlsx
+++ b/output/60bom_BOM_Report.xlsx
@@ -10,9 +10,9 @@
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Merge Candidate" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Capacitor Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Merge Workspace" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Capacitor Merge Workspace" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Resistor Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Resistor Detail" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Resistor Merge Workspace" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Resistor Nearby Value" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="AVL Candidate" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Risk Review" sheetId="9" state="visible" r:id="rId9"/>
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Merge Candidate'!$A$1:$M$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Capacitor Summary'!$A$1:$I$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Merge Workspace'!$A$1:$L$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Capacitor Merge Workspace'!$A$1:$L$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resistor Summary'!$A$1:$H$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Resistor Detail'!$A$1:$K$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Resistor Merge Workspace'!$A$1:$K$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Resistor Nearby Value'!$A$1:$H$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'AVL Candidate'!$A$1:$G$175</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Risk Review'!$A$1:$F$21</definedName>
@@ -780,7 +780,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Global health check: Dashboard shows scope; Summary queues review; RD records BOM Action in Merge Workspace.</t>
+          <t>Global health check: Dashboard shows scope; Summary queues review; RD records BOM Action in component Merge Workspaces.</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-24T09:03:29+00:00  |  Rules: E:\GitHub\BOM_Normalization_Tool\config\default_rules.json; runtime near-value override  |  Platform: 2.0.0</t>
+          <t>Generated: 2026-07-24T09:38:42+00:00  |  Rules: E:\GitHub\BOM_Normalization_Tool\config\default_rules.json; runtime near-value override  |  Platform: 2.0.0</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>2026-07-24T09:03:29+00:00</t>
+          <t>2026-07-24T09:38:42+00:00</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr"/>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="H2" s="16">
-        <f>IFERROR(IF(VLOOKUP($A2,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A2,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A2,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A2,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I2" s="19" t="inlineStr">
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="H3" s="15">
-        <f>IFERROR(IF(VLOOKUP($A3,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A3,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A3,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A3,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I3" s="19" t="inlineStr">
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="H4" s="16">
-        <f>IFERROR(IF(VLOOKUP($A4,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A4,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A4,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A4,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I4" s="19" t="inlineStr">
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="H5" s="15">
-        <f>IFERROR(IF(VLOOKUP($A5,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A5,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A5,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A5,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I5" s="19" t="inlineStr">
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="H6" s="16">
-        <f>IFERROR(IF(VLOOKUP($A6,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A6,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A6,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A6,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I6" s="19" t="inlineStr">
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="H7" s="15">
-        <f>IFERROR(IF(VLOOKUP($A7,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A7,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A7,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A7,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I7" s="19" t="inlineStr">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="H8" s="16">
-        <f>IFERROR(IF(VLOOKUP($A8,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A8,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A8,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A8,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I8" s="19" t="inlineStr">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="H9" s="15">
-        <f>IFERROR(IF(VLOOKUP($A9,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A9,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A9,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A9,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I9" s="19" t="inlineStr">
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="H10" s="16">
-        <f>IFERROR(IF(VLOOKUP($A10,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A10,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A10,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A10,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="H11" s="15">
-        <f>IFERROR(IF(VLOOKUP($A11,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A11,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A11,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A11,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I11" s="19" t="inlineStr">
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="H12" s="16">
-        <f>IFERROR(IF(VLOOKUP($A12,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A12,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A12,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A12,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I12" s="19" t="inlineStr">
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="H13" s="15">
-        <f>IFERROR(IF(VLOOKUP($A13,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A13,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A13,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A13,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I13" s="19" t="inlineStr">
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="H14" s="16">
-        <f>IFERROR(IF(VLOOKUP($A14,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A14,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A14,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A14,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I14" s="19" t="inlineStr">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="H15" s="15">
-        <f>IFERROR(IF(VLOOKUP($A15,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A15,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A15,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A15,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I15" s="19" t="inlineStr">
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="H16" s="16">
-        <f>IFERROR(IF(VLOOKUP($A16,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A16,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A16,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A16,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I16" s="19" t="inlineStr">
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="H17" s="15">
-        <f>IFERROR(IF(VLOOKUP($A17,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A17,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A17,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A17,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I17" s="19" t="inlineStr">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="H18" s="16">
-        <f>IFERROR(IF(VLOOKUP($A18,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A18,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A18,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A18,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I18" s="19" t="inlineStr">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="H19" s="15">
-        <f>IFERROR(IF(VLOOKUP($A19,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A19,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A19,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A19,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I19" s="19" t="inlineStr">
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="H20" s="16">
-        <f>IFERROR(IF(VLOOKUP($A20,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A20,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A20,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A20,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I20" s="19" t="inlineStr">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="H21" s="15">
-        <f>IFERROR(IF(VLOOKUP($A21,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A21,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A21,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A21,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I21" s="19" t="inlineStr">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="H22" s="16">
-        <f>IFERROR(IF(VLOOKUP($A22,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A22,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A22,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A22,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="H23" s="15">
-        <f>IFERROR(IF(VLOOKUP($A23,'Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A23,'Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($A23,'Capacitor Merge Workspace'!$A:$L,12,FALSE)="","Pending",VLOOKUP($A23,'Capacitor Merge Workspace'!$A:$L,12,FALSE)),"Pending")</f>
         <v/>
       </c>
       <c r="I23" s="19" t="inlineStr">
@@ -6238,7 +6238,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L68"/>
-  <conditionalFormatting sqref="L2:L68">
+  <conditionalFormatting sqref="L2:L1048576">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$L2="🟢 Merge"</formula>
     </cfRule>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="E2" s="16">
-        <f>IFERROR(IF(VLOOKUP($H2,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H2,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H2,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H2,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H2,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H2,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H2,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H2,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F2" s="16" t="inlineStr">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E3" s="15">
-        <f>IFERROR(IF(VLOOKUP($H3,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H3,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H3,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H3,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H3,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H3,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H3,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H3,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F3" s="15" t="inlineStr">
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="E4" s="16">
-        <f>IFERROR(IF(VLOOKUP($H4,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H4,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H4,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H4,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H4,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H4,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H4,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H4,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F4" s="16" t="inlineStr">
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="E5" s="15">
-        <f>IFERROR(IF(VLOOKUP($H5,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H5,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H5,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H5,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H5,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H5,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H5,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H5,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F5" s="15" t="inlineStr">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E6" s="16">
-        <f>IFERROR(IF(VLOOKUP($H6,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H6,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H6,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H6,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H6,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H6,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H6,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H6,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F6" s="16" t="inlineStr">
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="E7" s="15">
-        <f>IFERROR(IF(VLOOKUP($H7,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H7,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H7,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H7,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H7,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H7,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H7,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H7,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="E8" s="16">
-        <f>IFERROR(IF(VLOOKUP($H8,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H8,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H8,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H8,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H8,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H8,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H8,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H8,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>IFERROR(IF(VLOOKUP($H9,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H9,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H9,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H9,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H9,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H9,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H9,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H9,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="E10" s="16">
-        <f>IFERROR(IF(VLOOKUP($H10,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H10,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H10,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H10,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H10,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H10,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H10,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H10,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>IFERROR(IF(VLOOKUP($H11,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H11,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H11,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H11,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H11,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H11,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H11,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H11,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="E12" s="16">
-        <f>IFERROR(IF(VLOOKUP($H12,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H12,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H12,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H12,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H12,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H12,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H12,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H12,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F12" s="16" t="inlineStr">
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="E13" s="15">
-        <f>IFERROR(IF(VLOOKUP($H13,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H13,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H13,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H13,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H13,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H13,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H13,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H13,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="E14" s="16">
-        <f>IFERROR(IF(VLOOKUP($H14,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H14,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H14,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H14,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H14,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H14,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H14,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H14,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="E15" s="15">
-        <f>IFERROR(IF(VLOOKUP($H15,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H15,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H15,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H15,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H15,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H15,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H15,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H15,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F15" s="15" t="inlineStr">
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>IFERROR(IF(VLOOKUP($H16,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H16,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H16,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H16,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H16,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H16,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H16,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H16,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F16" s="16" t="inlineStr">
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="E17" s="15">
-        <f>IFERROR(IF(VLOOKUP($H17,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H17,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H17,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H17,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H17,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H17,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H17,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H17,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>IFERROR(IF(VLOOKUP($H18,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H18,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H18,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H18,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H18,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H18,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H18,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H18,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F18" s="16" t="inlineStr">
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="E19" s="15">
-        <f>IFERROR(IF(VLOOKUP($H19,'Resistor Detail'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H19,'Resistor Detail'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H19,'Resistor Detail'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H19,'Resistor Detail'!$A:$K,11,FALSE))),"Pending")</f>
+        <f>IFERROR(IF(VLOOKUP($H19,'Resistor Merge Workspace'!$A:$K,10,FALSE)="","Pending",VLOOKUP($H19,'Resistor Merge Workspace'!$A:$K,10,FALSE)&amp;IF(VLOOKUP($H19,'Resistor Merge Workspace'!$A:$K,11,FALSE)="",""," → "&amp;VLOOKUP($H19,'Resistor Merge Workspace'!$A:$K,11,FALSE))),"Pending")</f>
         <v/>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -7031,7 +7031,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H19"/>
-  <conditionalFormatting sqref="E2:E19">
+  <conditionalFormatting sqref="E2:E1048576">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT($E2,LEN("🟢 Merge"))="🟢 Merge"</formula>
     </cfRule>
@@ -11548,7 +11548,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K119"/>
-  <conditionalFormatting sqref="J2:J119">
+  <conditionalFormatting sqref="J2:J1048576">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J2="🟢 Merge"</formula>
     </cfRule>
